--- a/output/per_model_training_cost.xlsx
+++ b/output/per_model_training_cost.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="60">
   <si>
     <t>Model</t>
   </si>
@@ -127,6 +127,12 @@
     <t>GLM-4.5V</t>
   </si>
   <si>
+    <t>GLM-4.1V-Thinking</t>
+  </si>
+  <si>
+    <t>GLM-4.6</t>
+  </si>
+  <si>
     <t>CogVideoX</t>
   </si>
   <si>
@@ -179,6 +185,9 @@
   </si>
   <si>
     <t>2025-04</t>
+  </si>
+  <si>
+    <t>2025-09</t>
   </si>
   <si>
     <t>2024-10</t>
@@ -542,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -579,10 +588,10 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D2">
         <v>3.134631024224449E+24</v>
@@ -608,10 +617,10 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D3">
         <v>1.41E+23</v>
@@ -637,10 +646,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D4">
         <v>2.0655E+24</v>
@@ -666,10 +675,10 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D5">
         <v>2.756E+23</v>
@@ -695,10 +704,10 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D6">
         <v>1.378E+23</v>
@@ -724,10 +733,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D7">
         <v>6.460322012559246E+23</v>
@@ -753,10 +762,10 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D8">
         <v>6.832393305193044E+21</v>
@@ -782,10 +791,10 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D9">
         <v>6.748271087691732E+21</v>
@@ -811,10 +820,10 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D10">
         <v>2.093408295366517E+24</v>
@@ -840,10 +849,10 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D11">
         <v>3.087679891223758E+21</v>
@@ -869,10 +878,10 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D12">
         <v>2.244778901588034E+20</v>
@@ -898,10 +907,10 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D13">
         <v>2.194725548127136E+20</v>
@@ -927,10 +936,10 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D14">
         <v>6.997345090951331E+22</v>
@@ -956,10 +965,10 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D15">
         <v>1.547983611901956E+20</v>
@@ -985,10 +994,10 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D16">
         <v>1.027831421530397E+21</v>
@@ -1014,10 +1023,10 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D17">
         <v>2.122885865880202E+18</v>
@@ -1043,10 +1052,10 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D18">
         <v>6.2601276323116E+20</v>
@@ -1072,10 +1081,10 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D19">
         <v>1.18429371660984E+18</v>
@@ -1101,10 +1110,10 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D20">
         <v>1.249404943294399E+21</v>
@@ -1130,10 +1139,10 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D21">
         <v>2.620136777517372E+18</v>
@@ -1159,10 +1168,10 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D22">
         <v>9.67036168298893E+20</v>
@@ -1188,10 +1197,10 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D23">
         <v>1.78164448721092E+18</v>
@@ -1217,10 +1226,10 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D24">
         <v>4.411442917941959E+24</v>
@@ -1246,10 +1255,10 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D25">
         <v>1.651650053196938E+24</v>
@@ -1275,10 +1284,10 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D26">
         <v>2.873330307067346E+24</v>
@@ -1304,10 +1313,10 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D27">
         <v>8.083239367271508E+23</v>
@@ -1333,10 +1342,10 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D28">
         <v>2.187460613030667E+22</v>
@@ -1362,10 +1371,10 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D29">
         <v>1.44E+23</v>
@@ -1391,28 +1400,28 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C30" t="s">
         <v>55</v>
       </c>
       <c r="D30">
-        <v>1.647943581670982E+23</v>
+        <v>1.08E+23</v>
       </c>
       <c r="E30">
-        <v>4.703120521685389E+23</v>
+        <v>1.08E+23</v>
       </c>
       <c r="F30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30">
-        <v>0.32</v>
+        <v>0.14</v>
       </c>
       <c r="H30">
-        <v>0.79</v>
+        <v>0.28</v>
       </c>
       <c r="I30">
-        <v>1.87</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1420,28 +1429,28 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D31">
-        <v>1.640178900222697E+20</v>
+        <v>3.360767382307536E+22</v>
       </c>
       <c r="E31">
-        <v>2.81272812136205E+22</v>
+        <v>6.437813176872451E+23</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="H31">
-        <v>0.01</v>
+        <v>2.78</v>
       </c>
       <c r="I31">
-        <v>0.08</v>
+        <v>23.65</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1449,28 +1458,28 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D32">
-        <v>3.726903380802336E+20</v>
+        <v>1.650716613460357E+23</v>
       </c>
       <c r="E32">
-        <v>2.39388004628029E+22</v>
+        <v>4.700105071178299E+23</v>
       </c>
       <c r="F32" t="b">
         <v>0</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="H32">
-        <v>0.06</v>
+        <v>0.79</v>
       </c>
       <c r="I32">
-        <v>0.73</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1478,28 +1487,28 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C33" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D33">
-        <v>4.199012622563808E+22</v>
+        <v>1.676783905979122E+20</v>
       </c>
       <c r="E33">
-        <v>7.796750420080379E+22</v>
+        <v>2.843294854850235E+22</v>
       </c>
       <c r="F33" t="b">
         <v>0</v>
       </c>
       <c r="G33">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>0.15</v>
+        <v>0.01</v>
       </c>
       <c r="I33">
-        <v>0.33</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1507,16 +1516,16 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C34" t="s">
         <v>56</v>
       </c>
       <c r="D34">
-        <v>3.370879425518788E+19</v>
+        <v>3.74675907235E+20</v>
       </c>
       <c r="E34">
-        <v>5.20177198096969E+21</v>
+        <v>2.421170898324403E+22</v>
       </c>
       <c r="F34" t="b">
         <v>0</v>
@@ -1525,10 +1534,10 @@
         <v>0</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="I34">
-        <v>0.01</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1536,28 +1545,28 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C35" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D35">
-        <v>1.393918836598721E+23</v>
+        <v>4.197473984970759E+22</v>
       </c>
       <c r="E35">
-        <v>3.103050412767586E+23</v>
+        <v>7.796379539426555E+22</v>
       </c>
       <c r="F35" t="b">
         <v>0</v>
       </c>
       <c r="G35">
-        <v>0.25</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H35">
-        <v>0.57</v>
+        <v>0.15</v>
       </c>
       <c r="I35">
-        <v>1.26</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1565,27 +1574,85 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" t="s">
+        <v>59</v>
+      </c>
+      <c r="D36">
+        <v>3.332971405649743E+19</v>
+      </c>
+      <c r="E36">
+        <v>5.134970671176296E+21</v>
+      </c>
+      <c r="F36" t="b">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" t="s">
+        <v>48</v>
+      </c>
+      <c r="D37">
+        <v>1.396661772754924E+23</v>
+      </c>
+      <c r="E37">
+        <v>3.106803957178061E+23</v>
+      </c>
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0.25</v>
+      </c>
+      <c r="H37">
+        <v>0.57</v>
+      </c>
+      <c r="I37">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
         <v>45</v>
       </c>
-      <c r="C36" t="s">
-        <v>46</v>
-      </c>
-      <c r="D36">
-        <v>1.222356866086916E+20</v>
-      </c>
-      <c r="E36">
-        <v>1.944664392549831E+22</v>
-      </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-      <c r="I36">
+      <c r="B38" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38">
+        <v>1.164362885069952E+20</v>
+      </c>
+      <c r="E38">
+        <v>2.006078061871295E+22</v>
+      </c>
+      <c r="F38" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
         <v>0.06</v>
       </c>
     </row>

--- a/output/per_model_training_cost.xlsx
+++ b/output/per_model_training_cost.xlsx
@@ -480,22 +480,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.134631024224449e+24</v>
+        <v>3.256141008177746e+24</v>
       </c>
       <c r="E2" t="n">
-        <v>3.500097502594358e+24</v>
+        <v>3.662230379860482e+24</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>4.27</v>
+        <v>4.45</v>
       </c>
       <c r="H2" t="n">
-        <v>8.58</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>17.47</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="3">
@@ -1250,22 +1250,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4.411442917941988e+24</v>
+        <v>4.582570473446187e+24</v>
       </c>
       <c r="E24" t="n">
-        <v>4.918439675079785e+24</v>
+        <v>5.145908278639809e+24</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>5.99</v>
+        <v>6.24</v>
       </c>
       <c r="H24" t="n">
-        <v>12.09</v>
+        <v>12.61</v>
       </c>
       <c r="I24" t="n">
-        <v>24.24</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="25">
@@ -1285,22 +1285,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1.651650053196938e+24</v>
+        <v>1.715642339360417e+24</v>
       </c>
       <c r="E25" t="n">
-        <v>1.843252115319476e+24</v>
+        <v>1.92853390321369e+24</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="H25" t="n">
-        <v>4.53</v>
+        <v>4.72</v>
       </c>
       <c r="I25" t="n">
-        <v>9.109999999999999</v>
+        <v>9.51</v>
       </c>
     </row>
     <row r="26">
@@ -1320,22 +1320,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2.873330307067346e+24</v>
+        <v>2.984717093184786e+24</v>
       </c>
       <c r="E26" t="n">
-        <v>3.206665157683391e+24</v>
+        <v>3.355097445940775e+24</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>3.9</v>
+        <v>4.06</v>
       </c>
       <c r="H26" t="n">
-        <v>7.89</v>
+        <v>8.23</v>
       </c>
       <c r="I26" t="n">
-        <v>15.83</v>
+        <v>16.51</v>
       </c>
     </row>
     <row r="27">
@@ -1355,22 +1355,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>8.083239367271508e+23</v>
+        <v>8.39672861157054e+23</v>
       </c>
       <c r="E27" t="n">
-        <v>9.021099120348051e+23</v>
+        <v>9.438835769958571e+23</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="H27" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="I27" t="n">
-        <v>4.46</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="28">
@@ -1390,22 +1390,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1.296527263929647e+23</v>
+        <v>1.351534500567111e+23</v>
       </c>
       <c r="E28" t="n">
-        <v>5.298621369192508e+23</v>
+        <v>5.523237321457973e+23</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="H28" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="I28" t="n">
-        <v>5.3</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="29">
@@ -1495,22 +1495,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1.99222530434345e+23</v>
+        <v>2.075330677617413e+23</v>
       </c>
       <c r="E31" t="n">
-        <v>8.191265443231713e+23</v>
+        <v>8.546470737186588e+23</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="H31" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="I31" t="n">
-        <v>8.16</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="32">
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>8.382600903875923e+21</v>
+        <v>8.739657710855276e+21</v>
       </c>
       <c r="E34" t="n">
-        <v>6.143979797784222e+22</v>
+        <v>6.410490611390526e+22</v>
       </c>
       <c r="F34" t="b">
         <v>0</v>
@@ -1615,7 +1615,7 @@
         <v>0.14</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="35">

--- a/output/per_model_training_cost.xlsx
+++ b/output/per_model_training_cost.xlsx
@@ -734,13 +734,13 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="H9" t="n">
-        <v>0.52</v>
+        <v>0.34</v>
       </c>
       <c r="I9" t="n">
-        <v>1.87</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="10">
